--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbryer/SPS Dropbox/Jason Bryer/Teaching/IS381 2026 Spring/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/IS381 2026 Spring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA2D2142-1D55-144D-9BCE-C870CB90DA1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36D5DE53-4D12-F647-840A-3A547ED6B134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11680" yWindow="11120" windowWidth="24780" windowHeight="14160" xr2:uid="{BFE2A6F7-E8E8-014E-9460-2468D969C60C}"/>
+    <workbookView xWindow="5000" yWindow="11820" windowWidth="24780" windowHeight="14160" xr2:uid="{BFE2A6F7-E8E8-014E-9460-2468D969C60C}"/>
   </bookViews>
   <sheets>
     <sheet name="Schedule" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
   <si>
     <t>Week</t>
   </si>
@@ -44,9 +44,6 @@
     <t>End</t>
   </si>
   <si>
-    <t>Introduction to R and RStudio</t>
-  </si>
-  <si>
     <t>Data (importing and structure)</t>
   </si>
   <si>
@@ -198,6 +195,15 @@
   </si>
   <si>
     <t>NO CLASS - Spring Break</t>
+  </si>
+  <si>
+    <t>/slides/00-Intro_to_Course.html</t>
+  </si>
+  <si>
+    <t>Intro to the Course</t>
+  </si>
+  <si>
+    <t>B9FwyKNQOyA</t>
   </si>
 </sst>
 </file>
@@ -1109,25 +1115,25 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" t="s">
         <v>13</v>
       </c>
-      <c r="G1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>14</v>
       </c>
-      <c r="I1" t="s">
-        <v>15</v>
-      </c>
       <c r="J1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
@@ -1146,13 +1152,19 @@
         <v>46048</v>
       </c>
       <c r="E2" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="F2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G2" t="s">
-        <v>20</v>
+        <v>19</v>
+      </c>
+      <c r="H2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I2" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -1172,13 +1184,13 @@
         <v>46055</v>
       </c>
       <c r="E3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I3" s="4"/>
     </row>
@@ -1199,13 +1211,13 @@
         <v>46062</v>
       </c>
       <c r="E4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -1221,13 +1233,13 @@
         <v>46075</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -1247,13 +1259,13 @@
         <v>46076</v>
       </c>
       <c r="E6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -1273,13 +1285,13 @@
         <v>46083</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -1299,13 +1311,13 @@
         <v>46090</v>
       </c>
       <c r="E8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
@@ -1325,13 +1337,13 @@
         <v>46097</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
@@ -1351,13 +1363,13 @@
         <v>46104</v>
       </c>
       <c r="E10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
@@ -1377,13 +1389,13 @@
         <v>46111</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
@@ -1396,7 +1408,7 @@
         <v>46124</v>
       </c>
       <c r="E12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
@@ -1416,13 +1428,13 @@
         <v>46125</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
@@ -1442,13 +1454,13 @@
         <v>46132</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
@@ -1468,13 +1480,13 @@
         <v>46139</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
@@ -1494,13 +1506,13 @@
         <v>46146</v>
       </c>
       <c r="E16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
@@ -1520,10 +1532,10 @@
         <v>46153</v>
       </c>
       <c r="E17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/IS381 2026 Spring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36D5DE53-4D12-F647-840A-3A547ED6B134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFB4D5DC-26B2-AE43-8634-F6291CBE7702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5000" yWindow="11820" windowWidth="24780" windowHeight="14160" xr2:uid="{BFE2A6F7-E8E8-014E-9460-2468D969C60C}"/>
   </bookViews>
@@ -197,13 +197,13 @@
     <t>NO CLASS - Spring Break</t>
   </si>
   <si>
-    <t>/slides/00-Intro_to_Course.html</t>
-  </si>
-  <si>
     <t>Intro to the Course</t>
   </si>
   <si>
     <t>B9FwyKNQOyA</t>
+  </si>
+  <si>
+    <t>00-Intro_to_Course.html</t>
   </si>
 </sst>
 </file>
@@ -1152,7 +1152,7 @@
         <v>46048</v>
       </c>
       <c r="E2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F2" t="s">
         <v>33</v>
@@ -1161,10 +1161,10 @@
         <v>19</v>
       </c>
       <c r="H2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/IS381 2026 Spring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFB4D5DC-26B2-AE43-8634-F6291CBE7702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53FB4A37-ADBA-0E4C-8867-43C55367F5AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5000" yWindow="11820" windowWidth="24780" windowHeight="14160" xr2:uid="{BFE2A6F7-E8E8-014E-9460-2468D969C60C}"/>
   </bookViews>
@@ -203,7 +203,7 @@
     <t>B9FwyKNQOyA</t>
   </si>
   <si>
-    <t>00-Intro_to_Course.html</t>
+    <t>00-Intro_to_Course</t>
   </si>
 </sst>
 </file>

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/IS381 2026 Spring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53FB4A37-ADBA-0E4C-8867-43C55367F5AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{337CC40D-25BF-F843-B78A-EE7EB0B00625}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5000" yWindow="11820" windowWidth="24780" windowHeight="14160" xr2:uid="{BFE2A6F7-E8E8-014E-9460-2468D969C60C}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t>Week</t>
   </si>
@@ -98,9 +98,6 @@
     <t>/assignments/02_R_Coding_Basics.zip</t>
   </si>
   <si>
-    <t>/assignments/03_Data.zip</t>
-  </si>
-  <si>
     <t>/assignments/04_Data_Visualization.zip</t>
   </si>
   <si>
@@ -204,6 +201,12 @@
   </si>
   <si>
     <t>00-Intro_to_Course</t>
+  </si>
+  <si>
+    <t>01-Intro_to_Data</t>
+  </si>
+  <si>
+    <t>_rWAkQjxrOg</t>
   </si>
 </sst>
 </file>
@@ -1115,7 +1118,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E1" t="s">
         <v>18</v>
@@ -1133,7 +1136,7 @@
         <v>14</v>
       </c>
       <c r="J1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
@@ -1152,19 +1155,19 @@
         <v>46048</v>
       </c>
       <c r="E2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G2" t="s">
         <v>19</v>
       </c>
       <c r="H2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -1184,15 +1187,20 @@
         <v>46055</v>
       </c>
       <c r="E3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G3" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="4"/>
+      <c r="H3" t="s">
+        <v>56</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
@@ -1214,10 +1222,7 @@
         <v>3</v>
       </c>
       <c r="F4" t="s">
-        <v>36</v>
-      </c>
-      <c r="G4" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -1236,10 +1241,10 @@
         <v>4</v>
       </c>
       <c r="F5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -1259,13 +1264,13 @@
         <v>46076</v>
       </c>
       <c r="E6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -1288,10 +1293,10 @@
         <v>16</v>
       </c>
       <c r="F7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -1314,10 +1319,10 @@
         <v>17</v>
       </c>
       <c r="F8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
@@ -1340,10 +1345,10 @@
         <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
@@ -1363,13 +1368,13 @@
         <v>46104</v>
       </c>
       <c r="E10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
@@ -1392,10 +1397,10 @@
         <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
@@ -1408,7 +1413,7 @@
         <v>46124</v>
       </c>
       <c r="E12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
@@ -1431,10 +1436,10 @@
         <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
@@ -1457,10 +1462,10 @@
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
@@ -1483,10 +1488,10 @@
         <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
@@ -1509,10 +1514,10 @@
         <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
@@ -1535,7 +1540,7 @@
         <v>11</v>
       </c>
       <c r="F17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/IS381 2026 Spring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{337CC40D-25BF-F843-B78A-EE7EB0B00625}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{992877C8-8516-4E45-968A-700E494918E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5000" yWindow="11820" windowWidth="24780" windowHeight="14160" xr2:uid="{BFE2A6F7-E8E8-014E-9460-2468D969C60C}"/>
   </bookViews>
@@ -44,9 +44,6 @@
     <t>End</t>
   </si>
   <si>
-    <t>Data (importing and structure)</t>
-  </si>
-  <si>
     <t>Data visualization with ggplot2</t>
   </si>
   <si>
@@ -207,6 +204,9 @@
   </si>
   <si>
     <t>_rWAkQjxrOg</t>
+  </si>
+  <si>
+    <t>NO CLASS</t>
   </si>
 </sst>
 </file>
@@ -1118,25 +1118,25 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" t="s">
         <v>12</v>
       </c>
-      <c r="G1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>13</v>
       </c>
-      <c r="I1" t="s">
-        <v>14</v>
-      </c>
       <c r="J1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
@@ -1155,19 +1155,19 @@
         <v>46048</v>
       </c>
       <c r="E2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I2" t="s">
         <v>53</v>
-      </c>
-      <c r="F2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" t="s">
-        <v>55</v>
-      </c>
-      <c r="I2" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -1187,19 +1187,19 @@
         <v>46055</v>
       </c>
       <c r="E3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I3" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -1218,11 +1218,14 @@
         <f t="shared" si="1"/>
         <v>46062</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F4" t="s">
         <v>35</v>
+      </c>
+      <c r="G4" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -1237,14 +1240,11 @@
         <f t="shared" si="0"/>
         <v>46075</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>4</v>
+      <c r="E5" t="s">
+        <v>57</v>
       </c>
       <c r="F5" t="s">
-        <v>36</v>
-      </c>
-      <c r="G5" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -1264,13 +1264,13 @@
         <v>46076</v>
       </c>
       <c r="E6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -1290,13 +1290,13 @@
         <v>46083</v>
       </c>
       <c r="E7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -1316,13 +1316,13 @@
         <v>46090</v>
       </c>
       <c r="E8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
@@ -1342,13 +1342,13 @@
         <v>46097</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
@@ -1368,13 +1368,13 @@
         <v>46104</v>
       </c>
       <c r="E10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
@@ -1394,13 +1394,13 @@
         <v>46111</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
@@ -1413,7 +1413,7 @@
         <v>46124</v>
       </c>
       <c r="E12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
@@ -1433,13 +1433,13 @@
         <v>46125</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
@@ -1459,13 +1459,13 @@
         <v>46132</v>
       </c>
       <c r="E14" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
@@ -1485,13 +1485,13 @@
         <v>46139</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
@@ -1511,13 +1511,13 @@
         <v>46146</v>
       </c>
       <c r="E16" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
@@ -1537,10 +1537,10 @@
         <v>46153</v>
       </c>
       <c r="E17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/IS381 2026 Spring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{992877C8-8516-4E45-968A-700E494918E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F22C08DD-2DC5-0A44-BCC8-0504A1483652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5000" yWindow="11820" windowWidth="24780" windowHeight="14160" xr2:uid="{BFE2A6F7-E8E8-014E-9460-2468D969C60C}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t>Week</t>
   </si>
@@ -207,6 +207,12 @@
   </si>
   <si>
     <t>NO CLASS</t>
+  </si>
+  <si>
+    <t>1UI__xuCCkE</t>
+  </si>
+  <si>
+    <t>04-Data_Visualization</t>
   </si>
 </sst>
 </file>
@@ -1227,6 +1233,12 @@
       <c r="G4" t="s">
         <v>20</v>
       </c>
+      <c r="H4" t="s">
+        <v>59</v>
+      </c>
+      <c r="I4" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/IS381 2026 Spring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F22C08DD-2DC5-0A44-BCC8-0504A1483652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6408DC52-88BB-BE40-A006-0AF259782062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5000" yWindow="11820" windowWidth="24780" windowHeight="14160" xr2:uid="{BFE2A6F7-E8E8-014E-9460-2468D969C60C}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t>Week</t>
   </si>
@@ -213,6 +213,12 @@
   </si>
   <si>
     <t>04-Data_Visualization</t>
+  </si>
+  <si>
+    <t>05_Reshaping_Data</t>
+  </si>
+  <si>
+    <t>V_azBfjvkBA</t>
   </si>
 </sst>
 </file>
@@ -1284,6 +1290,12 @@
       <c r="G6" t="s">
         <v>21</v>
       </c>
+      <c r="H6" t="s">
+        <v>60</v>
+      </c>
+      <c r="I6" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/IS381 2026 Spring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6408DC52-88BB-BE40-A006-0AF259782062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74A7B0B3-C5FE-C141-B9F1-5A963DBA8B9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5000" yWindow="11820" windowWidth="24780" windowHeight="14160" xr2:uid="{BFE2A6F7-E8E8-014E-9460-2468D969C60C}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
   <si>
     <t>Week</t>
   </si>
@@ -219,6 +219,12 @@
   </si>
   <si>
     <t>V_azBfjvkBA</t>
+  </si>
+  <si>
+    <t>06-Probability</t>
+  </si>
+  <si>
+    <t>wIJV74NhoRU</t>
   </si>
 </sst>
 </file>
@@ -1322,6 +1328,12 @@
       <c r="G7" t="s">
         <v>22</v>
       </c>
+      <c r="H7" t="s">
+        <v>62</v>
+      </c>
+      <c r="I7" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/IS381 2026 Spring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74A7B0B3-C5FE-C141-B9F1-5A963DBA8B9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17B70F6E-3B4B-C349-9A30-190608D9C722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5000" yWindow="11820" windowWidth="24780" windowHeight="14160" xr2:uid="{BFE2A6F7-E8E8-014E-9460-2468D969C60C}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
   <si>
     <t>Week</t>
   </si>
@@ -225,6 +225,12 @@
   </si>
   <si>
     <t>wIJV74NhoRU</t>
+  </si>
+  <si>
+    <t>07-Distributions</t>
+  </si>
+  <si>
+    <t>GGLXCtG0fn0</t>
   </si>
 </sst>
 </file>
@@ -1360,6 +1366,12 @@
       <c r="G8" t="s">
         <v>23</v>
       </c>
+      <c r="H8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I8" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/IS381 2026 Spring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17B70F6E-3B4B-C349-9A30-190608D9C722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6FD9293-B7A2-1148-B94E-82CAF22FE9F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5000" yWindow="11820" windowWidth="24780" windowHeight="14160" xr2:uid="{BFE2A6F7-E8E8-014E-9460-2468D969C60C}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
   <si>
     <t>Week</t>
   </si>
@@ -231,6 +231,12 @@
   </si>
   <si>
     <t>GGLXCtG0fn0</t>
+  </si>
+  <si>
+    <t>08-Foundation_for_Inference</t>
+  </si>
+  <si>
+    <t>S-dUZRl59rk</t>
   </si>
 </sst>
 </file>
@@ -1398,6 +1404,12 @@
       <c r="G9" t="s">
         <v>24</v>
       </c>
+      <c r="H9" t="s">
+        <v>66</v>
+      </c>
+      <c r="I9" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/IS381 2026 Spring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6FD9293-B7A2-1148-B94E-82CAF22FE9F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{427D87C7-7A4C-3E47-A86C-2DAD5D86BB75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5000" yWindow="11820" windowWidth="24780" windowHeight="14160" xr2:uid="{BFE2A6F7-E8E8-014E-9460-2468D969C60C}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
   <si>
     <t>Week</t>
   </si>
@@ -237,6 +237,12 @@
   </si>
   <si>
     <t>S-dUZRl59rk</t>
+  </si>
+  <si>
+    <t>09-CLT_and_Boostrapping</t>
+  </si>
+  <si>
+    <t>FtdXKppT_6Q</t>
   </si>
 </sst>
 </file>
@@ -1436,6 +1442,12 @@
       <c r="G10" t="s">
         <v>25</v>
       </c>
+      <c r="H10" t="s">
+        <v>68</v>
+      </c>
+      <c r="I10" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/IS381 2026 Spring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{427D87C7-7A4C-3E47-A86C-2DAD5D86BB75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A106A3C-1C3A-EE4A-8DD3-7E95DFBA1680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5000" yWindow="11820" windowWidth="24780" windowHeight="14160" xr2:uid="{BFE2A6F7-E8E8-014E-9460-2468D969C60C}"/>
   </bookViews>
@@ -242,7 +242,7 @@
     <t>09-CLT_and_Boostrapping</t>
   </si>
   <si>
-    <t>FtdXKppT_6Q</t>
+    <t>AHVNMDD_0SE</t>
   </si>
 </sst>
 </file>

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/IS381 2026 Spring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A106A3C-1C3A-EE4A-8DD3-7E95DFBA1680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AE6FBF9-C978-0A4D-AF96-B8C40C8300E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5000" yWindow="11820" windowWidth="24780" windowHeight="14160" xr2:uid="{BFE2A6F7-E8E8-014E-9460-2468D969C60C}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
   <si>
     <t>Week</t>
   </si>
@@ -243,6 +243,12 @@
   </si>
   <si>
     <t>AHVNMDD_0SE</t>
+  </si>
+  <si>
+    <t>10-Inference_for_Proportions</t>
+  </si>
+  <si>
+    <t>hpgVln8Hvh0</t>
   </si>
 </sst>
 </file>
@@ -1474,6 +1480,12 @@
       <c r="G11" t="s">
         <v>26</v>
       </c>
+      <c r="H11" t="s">
+        <v>70</v>
+      </c>
+      <c r="I11" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B12" s="3">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/IS381 2026 Spring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AE6FBF9-C978-0A4D-AF96-B8C40C8300E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C36992C-6793-CA49-A0EC-EEB5436CA8B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5000" yWindow="11820" windowWidth="24780" windowHeight="14160" xr2:uid="{BFE2A6F7-E8E8-014E-9460-2468D969C60C}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
   <si>
     <t>Week</t>
   </si>
@@ -249,6 +249,12 @@
   </si>
   <si>
     <t>hpgVln8Hvh0</t>
+  </si>
+  <si>
+    <t>11-Two_way_tables</t>
+  </si>
+  <si>
+    <t>Qpm_PtsDho0</t>
   </si>
 </sst>
 </file>
@@ -1525,6 +1531,12 @@
       <c r="G13" t="s">
         <v>27</v>
       </c>
+      <c r="H13" t="s">
+        <v>72</v>
+      </c>
+      <c r="I13" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/IS381 2026 Spring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C36992C-6793-CA49-A0EC-EEB5436CA8B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B88FD0D6-50C1-BA41-BE19-8A7345E47A66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5000" yWindow="11820" windowWidth="24780" windowHeight="14160" xr2:uid="{BFE2A6F7-E8E8-014E-9460-2468D969C60C}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
   <si>
     <t>Week</t>
   </si>
@@ -255,6 +255,12 @@
   </si>
   <si>
     <t>Qpm_PtsDho0</t>
+  </si>
+  <si>
+    <t>12-Inference_for_Numerical_Data</t>
+  </si>
+  <si>
+    <t>xbRjqWvlGGc</t>
   </si>
 </sst>
 </file>
@@ -1563,6 +1569,12 @@
       <c r="G14" t="s">
         <v>28</v>
       </c>
+      <c r="H14" t="s">
+        <v>74</v>
+      </c>
+      <c r="I14" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/IS381 2026 Spring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B88FD0D6-50C1-BA41-BE19-8A7345E47A66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C730989-CC5D-DD49-9453-E8AB754E6E67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5000" yWindow="11820" windowWidth="24780" windowHeight="14160" xr2:uid="{BFE2A6F7-E8E8-014E-9460-2468D969C60C}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
   <si>
     <t>Week</t>
   </si>
@@ -261,6 +261,12 @@
   </si>
   <si>
     <t>xbRjqWvlGGc</t>
+  </si>
+  <si>
+    <t>13-ANOVA</t>
+  </si>
+  <si>
+    <t>o2Wxw84igT0</t>
   </si>
 </sst>
 </file>
@@ -1601,6 +1607,12 @@
       <c r="G15" t="s">
         <v>29</v>
       </c>
+      <c r="H15" t="s">
+        <v>76</v>
+      </c>
+      <c r="I15" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/IS381 2026 Spring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C730989-CC5D-DD49-9453-E8AB754E6E67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92A42EE6-0226-8C46-96F3-2593141E70EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5000" yWindow="11820" windowWidth="24780" windowHeight="14160" xr2:uid="{BFE2A6F7-E8E8-014E-9460-2468D969C60C}"/>
+    <workbookView xWindow="1580" yWindow="11760" windowWidth="24780" windowHeight="14160" xr2:uid="{BFE2A6F7-E8E8-014E-9460-2468D969C60C}"/>
   </bookViews>
   <sheets>
     <sheet name="Schedule" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
   <si>
     <t>Week</t>
   </si>
@@ -267,6 +267,12 @@
   </si>
   <si>
     <t>o2Wxw84igT0</t>
+  </si>
+  <si>
+    <t>14-Correlation</t>
+  </si>
+  <si>
+    <t>Cc4KiDL76YI</t>
   </si>
 </sst>
 </file>
@@ -1639,6 +1645,12 @@
       <c r="G16" t="s">
         <v>30</v>
       </c>
+      <c r="H16" t="s">
+        <v>78</v>
+      </c>
+      <c r="I16" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
